--- a/mappings/warehouses_mapping.xlsx
+++ b/mappings/warehouses_mapping.xlsx
@@ -60,12 +60,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -557,7 +557,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -593,7 +593,7 @@
           <t>Edm.String</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -631,7 +631,7 @@
           <t>Edm.String</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -753,7 +753,7 @@
           <t>Edm.Byte</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -791,7 +791,7 @@
           <t>Edm.Int32</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -829,7 +829,7 @@
           <t>Edm.DateTime</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -909,7 +909,7 @@
           <t>Edm.DateTime</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Custom</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
           <t>Edm.String</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -1338,7 +1338,7 @@
           <t>Edm.String</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -1418,7 +1418,7 @@
           <t>Edm.Byte</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -1456,7 +1456,7 @@
           <t>Edm.Byte</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -1494,7 +1494,7 @@
           <t>Edm.Guid</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -1532,7 +1532,7 @@
           <t>Edm.String</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -1570,7 +1570,7 @@
           <t>Edm.Guid</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
@@ -1608,7 +1608,7 @@
           <t>Edm.DateTime</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
@@ -1688,7 +1688,7 @@
           <t>Edm.DateTime</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
